--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8247422680412371</v>
+        <v>0.8041237113402062</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7605633802816901</v>
+        <v>0.7464788732394366</v>
       </c>
       <c r="D2">
-        <v>0.2982456140350877</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="E2">
         <v>97</v>
